--- a/docs/STM32L051_Modbus_配置地址表_v2.3.xlsx
+++ b/docs/STM32L051_Modbus_配置地址表_v2.3.xlsx
@@ -95,7 +95,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -109,11 +109,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -137,6 +165,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -502,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -558,11 +588,11 @@
           <t>UART2 / Modbus 物理层参数</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -762,11 +792,11 @@
           <t>系统参数</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -870,11 +900,11 @@
           <t>UART1 / 数据上报参数</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -946,11 +976,11 @@
           <t>设备本体信息</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1304,12 +1334,358 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>设备运行状态</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>0x0016</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>uptime_lo</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>0~65535</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>设备运行时间低 16 位 (秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>0x0017</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>uptime_hi</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>0~65535</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>设备运行时间高 16 位 (秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>预留寄存器 (未来扩展)</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>0x0018</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>reserved[0]</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>预留 #0 (只读, 返回 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>0x0019</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>reserved[1]</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>预留 #1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>0x001A</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>reserved[2]</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>预留 #2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>0x001B</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>reserved[3]</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>预留 #3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>0x001C</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>reserved[4]</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>预留 #4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>0x001D</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>reserved[5]</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>预留 #5</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>0x001E</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>reserved[6]</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>预留 #6</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>0x001F</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>reserved[7]</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>预留 #7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A30:F30"/>
     <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1384,12 +1760,12 @@
           <t>从机 0 (基地址 0x0100)</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="9" t="n"/>
+      <c r="G4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -1922,12 +2298,12 @@
           <t>从机 1 (基地址 0x0300)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -2460,12 +2836,12 @@
           <t>从机 2 (基地址 0x0500)</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="n"/>
-      <c r="G36" s="3" t="n"/>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -2998,12 +3374,12 @@
           <t>从机 3 (基地址 0x0700)</t>
         </is>
       </c>
-      <c r="B52" s="3" t="n"/>
-      <c r="C52" s="3" t="n"/>
-      <c r="D52" s="3" t="n"/>
-      <c r="E52" s="3" t="n"/>
-      <c r="F52" s="3" t="n"/>
-      <c r="G52" s="3" t="n"/>
+      <c r="B52" s="9" t="n"/>
+      <c r="C52" s="9" t="n"/>
+      <c r="D52" s="9" t="n"/>
+      <c r="E52" s="9" t="n"/>
+      <c r="F52" s="9" t="n"/>
+      <c r="G52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -3536,12 +3912,12 @@
           <t>从机 4 (基地址 0x0900)</t>
         </is>
       </c>
-      <c r="B68" s="3" t="n"/>
-      <c r="C68" s="3" t="n"/>
-      <c r="D68" s="3" t="n"/>
-      <c r="E68" s="3" t="n"/>
-      <c r="F68" s="3" t="n"/>
-      <c r="G68" s="3" t="n"/>
+      <c r="B68" s="9" t="n"/>
+      <c r="C68" s="9" t="n"/>
+      <c r="D68" s="9" t="n"/>
+      <c r="E68" s="9" t="n"/>
+      <c r="F68" s="9" t="n"/>
+      <c r="G68" s="10" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -4155,13 +4531,13 @@
           <t>从机 0 (基地址 0x0100)</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="9" t="n"/>
+      <c r="G4" s="9" t="n"/>
+      <c r="H4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -4169,13 +4545,13 @@
           <t xml:space="preserve">  数据点 0 (基地址 0x0110)</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
-      <c r="H5" s="8" t="n"/>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="n"/>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -4677,13 +5053,13 @@
           <t xml:space="preserve">  数据点 1 (基地址 0x0120)</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -5185,13 +5561,13 @@
           <t xml:space="preserve">  数据点 2 (基地址 0x0130)</t>
         </is>
       </c>
-      <c r="B33" s="8" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="8" t="n"/>
-      <c r="G33" s="8" t="n"/>
-      <c r="H33" s="8" t="n"/>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -5693,13 +6069,13 @@
           <t xml:space="preserve">  数据点 3 (基地址 0x0140)</t>
         </is>
       </c>
-      <c r="B47" s="8" t="n"/>
-      <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
-      <c r="E47" s="8" t="n"/>
-      <c r="F47" s="8" t="n"/>
-      <c r="G47" s="8" t="n"/>
-      <c r="H47" s="8" t="n"/>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="9" t="n"/>
+      <c r="H47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -6201,13 +6577,13 @@
           <t xml:space="preserve">  数据点 4 (基地址 0x0150)</t>
         </is>
       </c>
-      <c r="B61" s="8" t="n"/>
-      <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="n"/>
-      <c r="E61" s="8" t="n"/>
-      <c r="F61" s="8" t="n"/>
-      <c r="G61" s="8" t="n"/>
-      <c r="H61" s="8" t="n"/>
+      <c r="B61" s="9" t="n"/>
+      <c r="C61" s="9" t="n"/>
+      <c r="D61" s="9" t="n"/>
+      <c r="E61" s="9" t="n"/>
+      <c r="F61" s="9" t="n"/>
+      <c r="G61" s="9" t="n"/>
+      <c r="H61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -6709,13 +7085,13 @@
           <t xml:space="preserve">  数据点 5 (基地址 0x0160)</t>
         </is>
       </c>
-      <c r="B75" s="8" t="n"/>
-      <c r="C75" s="8" t="n"/>
-      <c r="D75" s="8" t="n"/>
-      <c r="E75" s="8" t="n"/>
-      <c r="F75" s="8" t="n"/>
-      <c r="G75" s="8" t="n"/>
-      <c r="H75" s="8" t="n"/>
+      <c r="B75" s="9" t="n"/>
+      <c r="C75" s="9" t="n"/>
+      <c r="D75" s="9" t="n"/>
+      <c r="E75" s="9" t="n"/>
+      <c r="F75" s="9" t="n"/>
+      <c r="G75" s="9" t="n"/>
+      <c r="H75" s="10" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
@@ -7217,13 +7593,13 @@
           <t xml:space="preserve">  数据点 6 (基地址 0x0170)</t>
         </is>
       </c>
-      <c r="B89" s="8" t="n"/>
-      <c r="C89" s="8" t="n"/>
-      <c r="D89" s="8" t="n"/>
-      <c r="E89" s="8" t="n"/>
-      <c r="F89" s="8" t="n"/>
-      <c r="G89" s="8" t="n"/>
-      <c r="H89" s="8" t="n"/>
+      <c r="B89" s="9" t="n"/>
+      <c r="C89" s="9" t="n"/>
+      <c r="D89" s="9" t="n"/>
+      <c r="E89" s="9" t="n"/>
+      <c r="F89" s="9" t="n"/>
+      <c r="G89" s="9" t="n"/>
+      <c r="H89" s="10" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
@@ -7725,13 +8101,13 @@
           <t xml:space="preserve">  数据点 7 (基地址 0x0180)</t>
         </is>
       </c>
-      <c r="B103" s="8" t="n"/>
-      <c r="C103" s="8" t="n"/>
-      <c r="D103" s="8" t="n"/>
-      <c r="E103" s="8" t="n"/>
-      <c r="F103" s="8" t="n"/>
-      <c r="G103" s="8" t="n"/>
-      <c r="H103" s="8" t="n"/>
+      <c r="B103" s="9" t="n"/>
+      <c r="C103" s="9" t="n"/>
+      <c r="D103" s="9" t="n"/>
+      <c r="E103" s="9" t="n"/>
+      <c r="F103" s="9" t="n"/>
+      <c r="G103" s="9" t="n"/>
+      <c r="H103" s="10" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="4" t="n">
@@ -8233,13 +8609,13 @@
           <t>从机 1 (基地址 0x0300)</t>
         </is>
       </c>
-      <c r="B117" s="3" t="n"/>
-      <c r="C117" s="3" t="n"/>
-      <c r="D117" s="3" t="n"/>
-      <c r="E117" s="3" t="n"/>
-      <c r="F117" s="3" t="n"/>
-      <c r="G117" s="3" t="n"/>
-      <c r="H117" s="3" t="n"/>
+      <c r="B117" s="9" t="n"/>
+      <c r="C117" s="9" t="n"/>
+      <c r="D117" s="9" t="n"/>
+      <c r="E117" s="9" t="n"/>
+      <c r="F117" s="9" t="n"/>
+      <c r="G117" s="9" t="n"/>
+      <c r="H117" s="10" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
@@ -8247,13 +8623,13 @@
           <t xml:space="preserve">  数据点 0 (基地址 0x0310)</t>
         </is>
       </c>
-      <c r="B118" s="8" t="n"/>
-      <c r="C118" s="8" t="n"/>
-      <c r="D118" s="8" t="n"/>
-      <c r="E118" s="8" t="n"/>
-      <c r="F118" s="8" t="n"/>
-      <c r="G118" s="8" t="n"/>
-      <c r="H118" s="8" t="n"/>
+      <c r="B118" s="9" t="n"/>
+      <c r="C118" s="9" t="n"/>
+      <c r="D118" s="9" t="n"/>
+      <c r="E118" s="9" t="n"/>
+      <c r="F118" s="9" t="n"/>
+      <c r="G118" s="9" t="n"/>
+      <c r="H118" s="10" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="n">
@@ -8755,13 +9131,13 @@
           <t xml:space="preserve">  数据点 1 (基地址 0x0320)</t>
         </is>
       </c>
-      <c r="B132" s="8" t="n"/>
-      <c r="C132" s="8" t="n"/>
-      <c r="D132" s="8" t="n"/>
-      <c r="E132" s="8" t="n"/>
-      <c r="F132" s="8" t="n"/>
-      <c r="G132" s="8" t="n"/>
-      <c r="H132" s="8" t="n"/>
+      <c r="B132" s="9" t="n"/>
+      <c r="C132" s="9" t="n"/>
+      <c r="D132" s="9" t="n"/>
+      <c r="E132" s="9" t="n"/>
+      <c r="F132" s="9" t="n"/>
+      <c r="G132" s="9" t="n"/>
+      <c r="H132" s="10" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="n">
@@ -9263,13 +9639,13 @@
           <t xml:space="preserve">  数据点 2 (基地址 0x0330)</t>
         </is>
       </c>
-      <c r="B146" s="8" t="n"/>
-      <c r="C146" s="8" t="n"/>
-      <c r="D146" s="8" t="n"/>
-      <c r="E146" s="8" t="n"/>
-      <c r="F146" s="8" t="n"/>
-      <c r="G146" s="8" t="n"/>
-      <c r="H146" s="8" t="n"/>
+      <c r="B146" s="9" t="n"/>
+      <c r="C146" s="9" t="n"/>
+      <c r="D146" s="9" t="n"/>
+      <c r="E146" s="9" t="n"/>
+      <c r="F146" s="9" t="n"/>
+      <c r="G146" s="9" t="n"/>
+      <c r="H146" s="10" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="4" t="n">
@@ -9771,13 +10147,13 @@
           <t xml:space="preserve">  数据点 3 (基地址 0x0340)</t>
         </is>
       </c>
-      <c r="B160" s="8" t="n"/>
-      <c r="C160" s="8" t="n"/>
-      <c r="D160" s="8" t="n"/>
-      <c r="E160" s="8" t="n"/>
-      <c r="F160" s="8" t="n"/>
-      <c r="G160" s="8" t="n"/>
-      <c r="H160" s="8" t="n"/>
+      <c r="B160" s="9" t="n"/>
+      <c r="C160" s="9" t="n"/>
+      <c r="D160" s="9" t="n"/>
+      <c r="E160" s="9" t="n"/>
+      <c r="F160" s="9" t="n"/>
+      <c r="G160" s="9" t="n"/>
+      <c r="H160" s="10" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="n">
@@ -10279,13 +10655,13 @@
           <t xml:space="preserve">  数据点 4 (基地址 0x0350)</t>
         </is>
       </c>
-      <c r="B174" s="8" t="n"/>
-      <c r="C174" s="8" t="n"/>
-      <c r="D174" s="8" t="n"/>
-      <c r="E174" s="8" t="n"/>
-      <c r="F174" s="8" t="n"/>
-      <c r="G174" s="8" t="n"/>
-      <c r="H174" s="8" t="n"/>
+      <c r="B174" s="9" t="n"/>
+      <c r="C174" s="9" t="n"/>
+      <c r="D174" s="9" t="n"/>
+      <c r="E174" s="9" t="n"/>
+      <c r="F174" s="9" t="n"/>
+      <c r="G174" s="9" t="n"/>
+      <c r="H174" s="10" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="4" t="n">
@@ -10787,13 +11163,13 @@
           <t xml:space="preserve">  数据点 5 (基地址 0x0360)</t>
         </is>
       </c>
-      <c r="B188" s="8" t="n"/>
-      <c r="C188" s="8" t="n"/>
-      <c r="D188" s="8" t="n"/>
-      <c r="E188" s="8" t="n"/>
-      <c r="F188" s="8" t="n"/>
-      <c r="G188" s="8" t="n"/>
-      <c r="H188" s="8" t="n"/>
+      <c r="B188" s="9" t="n"/>
+      <c r="C188" s="9" t="n"/>
+      <c r="D188" s="9" t="n"/>
+      <c r="E188" s="9" t="n"/>
+      <c r="F188" s="9" t="n"/>
+      <c r="G188" s="9" t="n"/>
+      <c r="H188" s="10" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="4" t="n">
@@ -11295,13 +11671,13 @@
           <t xml:space="preserve">  数据点 6 (基地址 0x0370)</t>
         </is>
       </c>
-      <c r="B202" s="8" t="n"/>
-      <c r="C202" s="8" t="n"/>
-      <c r="D202" s="8" t="n"/>
-      <c r="E202" s="8" t="n"/>
-      <c r="F202" s="8" t="n"/>
-      <c r="G202" s="8" t="n"/>
-      <c r="H202" s="8" t="n"/>
+      <c r="B202" s="9" t="n"/>
+      <c r="C202" s="9" t="n"/>
+      <c r="D202" s="9" t="n"/>
+      <c r="E202" s="9" t="n"/>
+      <c r="F202" s="9" t="n"/>
+      <c r="G202" s="9" t="n"/>
+      <c r="H202" s="10" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="4" t="n">
@@ -11803,13 +12179,13 @@
           <t xml:space="preserve">  数据点 7 (基地址 0x0380)</t>
         </is>
       </c>
-      <c r="B216" s="8" t="n"/>
-      <c r="C216" s="8" t="n"/>
-      <c r="D216" s="8" t="n"/>
-      <c r="E216" s="8" t="n"/>
-      <c r="F216" s="8" t="n"/>
-      <c r="G216" s="8" t="n"/>
-      <c r="H216" s="8" t="n"/>
+      <c r="B216" s="9" t="n"/>
+      <c r="C216" s="9" t="n"/>
+      <c r="D216" s="9" t="n"/>
+      <c r="E216" s="9" t="n"/>
+      <c r="F216" s="9" t="n"/>
+      <c r="G216" s="9" t="n"/>
+      <c r="H216" s="10" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="4" t="n">
@@ -12311,13 +12687,13 @@
           <t>从机 2 (基地址 0x0500)</t>
         </is>
       </c>
-      <c r="B230" s="3" t="n"/>
-      <c r="C230" s="3" t="n"/>
-      <c r="D230" s="3" t="n"/>
-      <c r="E230" s="3" t="n"/>
-      <c r="F230" s="3" t="n"/>
-      <c r="G230" s="3" t="n"/>
-      <c r="H230" s="3" t="n"/>
+      <c r="B230" s="9" t="n"/>
+      <c r="C230" s="9" t="n"/>
+      <c r="D230" s="9" t="n"/>
+      <c r="E230" s="9" t="n"/>
+      <c r="F230" s="9" t="n"/>
+      <c r="G230" s="9" t="n"/>
+      <c r="H230" s="10" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="8" t="inlineStr">
@@ -12325,13 +12701,13 @@
           <t xml:space="preserve">  数据点 0 (基地址 0x0510)</t>
         </is>
       </c>
-      <c r="B231" s="8" t="n"/>
-      <c r="C231" s="8" t="n"/>
-      <c r="D231" s="8" t="n"/>
-      <c r="E231" s="8" t="n"/>
-      <c r="F231" s="8" t="n"/>
-      <c r="G231" s="8" t="n"/>
-      <c r="H231" s="8" t="n"/>
+      <c r="B231" s="9" t="n"/>
+      <c r="C231" s="9" t="n"/>
+      <c r="D231" s="9" t="n"/>
+      <c r="E231" s="9" t="n"/>
+      <c r="F231" s="9" t="n"/>
+      <c r="G231" s="9" t="n"/>
+      <c r="H231" s="10" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="4" t="n">
@@ -12833,13 +13209,13 @@
           <t xml:space="preserve">  数据点 1 (基地址 0x0520)</t>
         </is>
       </c>
-      <c r="B245" s="8" t="n"/>
-      <c r="C245" s="8" t="n"/>
-      <c r="D245" s="8" t="n"/>
-      <c r="E245" s="8" t="n"/>
-      <c r="F245" s="8" t="n"/>
-      <c r="G245" s="8" t="n"/>
-      <c r="H245" s="8" t="n"/>
+      <c r="B245" s="9" t="n"/>
+      <c r="C245" s="9" t="n"/>
+      <c r="D245" s="9" t="n"/>
+      <c r="E245" s="9" t="n"/>
+      <c r="F245" s="9" t="n"/>
+      <c r="G245" s="9" t="n"/>
+      <c r="H245" s="10" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="4" t="n">
@@ -13341,13 +13717,13 @@
           <t xml:space="preserve">  数据点 2 (基地址 0x0530)</t>
         </is>
       </c>
-      <c r="B259" s="8" t="n"/>
-      <c r="C259" s="8" t="n"/>
-      <c r="D259" s="8" t="n"/>
-      <c r="E259" s="8" t="n"/>
-      <c r="F259" s="8" t="n"/>
-      <c r="G259" s="8" t="n"/>
-      <c r="H259" s="8" t="n"/>
+      <c r="B259" s="9" t="n"/>
+      <c r="C259" s="9" t="n"/>
+      <c r="D259" s="9" t="n"/>
+      <c r="E259" s="9" t="n"/>
+      <c r="F259" s="9" t="n"/>
+      <c r="G259" s="9" t="n"/>
+      <c r="H259" s="10" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="4" t="n">
@@ -13849,13 +14225,13 @@
           <t xml:space="preserve">  数据点 3 (基地址 0x0540)</t>
         </is>
       </c>
-      <c r="B273" s="8" t="n"/>
-      <c r="C273" s="8" t="n"/>
-      <c r="D273" s="8" t="n"/>
-      <c r="E273" s="8" t="n"/>
-      <c r="F273" s="8" t="n"/>
-      <c r="G273" s="8" t="n"/>
-      <c r="H273" s="8" t="n"/>
+      <c r="B273" s="9" t="n"/>
+      <c r="C273" s="9" t="n"/>
+      <c r="D273" s="9" t="n"/>
+      <c r="E273" s="9" t="n"/>
+      <c r="F273" s="9" t="n"/>
+      <c r="G273" s="9" t="n"/>
+      <c r="H273" s="10" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="4" t="n">
@@ -14357,13 +14733,13 @@
           <t xml:space="preserve">  数据点 4 (基地址 0x0550)</t>
         </is>
       </c>
-      <c r="B287" s="8" t="n"/>
-      <c r="C287" s="8" t="n"/>
-      <c r="D287" s="8" t="n"/>
-      <c r="E287" s="8" t="n"/>
-      <c r="F287" s="8" t="n"/>
-      <c r="G287" s="8" t="n"/>
-      <c r="H287" s="8" t="n"/>
+      <c r="B287" s="9" t="n"/>
+      <c r="C287" s="9" t="n"/>
+      <c r="D287" s="9" t="n"/>
+      <c r="E287" s="9" t="n"/>
+      <c r="F287" s="9" t="n"/>
+      <c r="G287" s="9" t="n"/>
+      <c r="H287" s="10" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="4" t="n">
@@ -14865,13 +15241,13 @@
           <t xml:space="preserve">  数据点 5 (基地址 0x0560)</t>
         </is>
       </c>
-      <c r="B301" s="8" t="n"/>
-      <c r="C301" s="8" t="n"/>
-      <c r="D301" s="8" t="n"/>
-      <c r="E301" s="8" t="n"/>
-      <c r="F301" s="8" t="n"/>
-      <c r="G301" s="8" t="n"/>
-      <c r="H301" s="8" t="n"/>
+      <c r="B301" s="9" t="n"/>
+      <c r="C301" s="9" t="n"/>
+      <c r="D301" s="9" t="n"/>
+      <c r="E301" s="9" t="n"/>
+      <c r="F301" s="9" t="n"/>
+      <c r="G301" s="9" t="n"/>
+      <c r="H301" s="10" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="4" t="n">
@@ -15373,13 +15749,13 @@
           <t xml:space="preserve">  数据点 6 (基地址 0x0570)</t>
         </is>
       </c>
-      <c r="B315" s="8" t="n"/>
-      <c r="C315" s="8" t="n"/>
-      <c r="D315" s="8" t="n"/>
-      <c r="E315" s="8" t="n"/>
-      <c r="F315" s="8" t="n"/>
-      <c r="G315" s="8" t="n"/>
-      <c r="H315" s="8" t="n"/>
+      <c r="B315" s="9" t="n"/>
+      <c r="C315" s="9" t="n"/>
+      <c r="D315" s="9" t="n"/>
+      <c r="E315" s="9" t="n"/>
+      <c r="F315" s="9" t="n"/>
+      <c r="G315" s="9" t="n"/>
+      <c r="H315" s="10" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="4" t="n">
@@ -15881,13 +16257,13 @@
           <t xml:space="preserve">  数据点 7 (基地址 0x0580)</t>
         </is>
       </c>
-      <c r="B329" s="8" t="n"/>
-      <c r="C329" s="8" t="n"/>
-      <c r="D329" s="8" t="n"/>
-      <c r="E329" s="8" t="n"/>
-      <c r="F329" s="8" t="n"/>
-      <c r="G329" s="8" t="n"/>
-      <c r="H329" s="8" t="n"/>
+      <c r="B329" s="9" t="n"/>
+      <c r="C329" s="9" t="n"/>
+      <c r="D329" s="9" t="n"/>
+      <c r="E329" s="9" t="n"/>
+      <c r="F329" s="9" t="n"/>
+      <c r="G329" s="9" t="n"/>
+      <c r="H329" s="10" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="4" t="n">
@@ -16389,13 +16765,13 @@
           <t>从机 3 (基地址 0x0700)</t>
         </is>
       </c>
-      <c r="B343" s="3" t="n"/>
-      <c r="C343" s="3" t="n"/>
-      <c r="D343" s="3" t="n"/>
-      <c r="E343" s="3" t="n"/>
-      <c r="F343" s="3" t="n"/>
-      <c r="G343" s="3" t="n"/>
-      <c r="H343" s="3" t="n"/>
+      <c r="B343" s="9" t="n"/>
+      <c r="C343" s="9" t="n"/>
+      <c r="D343" s="9" t="n"/>
+      <c r="E343" s="9" t="n"/>
+      <c r="F343" s="9" t="n"/>
+      <c r="G343" s="9" t="n"/>
+      <c r="H343" s="10" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="8" t="inlineStr">
@@ -16403,13 +16779,13 @@
           <t xml:space="preserve">  数据点 0 (基地址 0x0710)</t>
         </is>
       </c>
-      <c r="B344" s="8" t="n"/>
-      <c r="C344" s="8" t="n"/>
-      <c r="D344" s="8" t="n"/>
-      <c r="E344" s="8" t="n"/>
-      <c r="F344" s="8" t="n"/>
-      <c r="G344" s="8" t="n"/>
-      <c r="H344" s="8" t="n"/>
+      <c r="B344" s="9" t="n"/>
+      <c r="C344" s="9" t="n"/>
+      <c r="D344" s="9" t="n"/>
+      <c r="E344" s="9" t="n"/>
+      <c r="F344" s="9" t="n"/>
+      <c r="G344" s="9" t="n"/>
+      <c r="H344" s="10" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="4" t="n">
@@ -16911,13 +17287,13 @@
           <t xml:space="preserve">  数据点 1 (基地址 0x0720)</t>
         </is>
       </c>
-      <c r="B358" s="8" t="n"/>
-      <c r="C358" s="8" t="n"/>
-      <c r="D358" s="8" t="n"/>
-      <c r="E358" s="8" t="n"/>
-      <c r="F358" s="8" t="n"/>
-      <c r="G358" s="8" t="n"/>
-      <c r="H358" s="8" t="n"/>
+      <c r="B358" s="9" t="n"/>
+      <c r="C358" s="9" t="n"/>
+      <c r="D358" s="9" t="n"/>
+      <c r="E358" s="9" t="n"/>
+      <c r="F358" s="9" t="n"/>
+      <c r="G358" s="9" t="n"/>
+      <c r="H358" s="10" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="4" t="n">
@@ -17419,13 +17795,13 @@
           <t xml:space="preserve">  数据点 2 (基地址 0x0730)</t>
         </is>
       </c>
-      <c r="B372" s="8" t="n"/>
-      <c r="C372" s="8" t="n"/>
-      <c r="D372" s="8" t="n"/>
-      <c r="E372" s="8" t="n"/>
-      <c r="F372" s="8" t="n"/>
-      <c r="G372" s="8" t="n"/>
-      <c r="H372" s="8" t="n"/>
+      <c r="B372" s="9" t="n"/>
+      <c r="C372" s="9" t="n"/>
+      <c r="D372" s="9" t="n"/>
+      <c r="E372" s="9" t="n"/>
+      <c r="F372" s="9" t="n"/>
+      <c r="G372" s="9" t="n"/>
+      <c r="H372" s="10" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="4" t="n">
@@ -17927,13 +18303,13 @@
           <t xml:space="preserve">  数据点 3 (基地址 0x0740)</t>
         </is>
       </c>
-      <c r="B386" s="8" t="n"/>
-      <c r="C386" s="8" t="n"/>
-      <c r="D386" s="8" t="n"/>
-      <c r="E386" s="8" t="n"/>
-      <c r="F386" s="8" t="n"/>
-      <c r="G386" s="8" t="n"/>
-      <c r="H386" s="8" t="n"/>
+      <c r="B386" s="9" t="n"/>
+      <c r="C386" s="9" t="n"/>
+      <c r="D386" s="9" t="n"/>
+      <c r="E386" s="9" t="n"/>
+      <c r="F386" s="9" t="n"/>
+      <c r="G386" s="9" t="n"/>
+      <c r="H386" s="10" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="4" t="n">
@@ -18435,13 +18811,13 @@
           <t xml:space="preserve">  数据点 4 (基地址 0x0750)</t>
         </is>
       </c>
-      <c r="B400" s="8" t="n"/>
-      <c r="C400" s="8" t="n"/>
-      <c r="D400" s="8" t="n"/>
-      <c r="E400" s="8" t="n"/>
-      <c r="F400" s="8" t="n"/>
-      <c r="G400" s="8" t="n"/>
-      <c r="H400" s="8" t="n"/>
+      <c r="B400" s="9" t="n"/>
+      <c r="C400" s="9" t="n"/>
+      <c r="D400" s="9" t="n"/>
+      <c r="E400" s="9" t="n"/>
+      <c r="F400" s="9" t="n"/>
+      <c r="G400" s="9" t="n"/>
+      <c r="H400" s="10" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="4" t="n">
@@ -18943,13 +19319,13 @@
           <t xml:space="preserve">  数据点 5 (基地址 0x0760)</t>
         </is>
       </c>
-      <c r="B414" s="8" t="n"/>
-      <c r="C414" s="8" t="n"/>
-      <c r="D414" s="8" t="n"/>
-      <c r="E414" s="8" t="n"/>
-      <c r="F414" s="8" t="n"/>
-      <c r="G414" s="8" t="n"/>
-      <c r="H414" s="8" t="n"/>
+      <c r="B414" s="9" t="n"/>
+      <c r="C414" s="9" t="n"/>
+      <c r="D414" s="9" t="n"/>
+      <c r="E414" s="9" t="n"/>
+      <c r="F414" s="9" t="n"/>
+      <c r="G414" s="9" t="n"/>
+      <c r="H414" s="10" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="4" t="n">
@@ -19451,13 +19827,13 @@
           <t xml:space="preserve">  数据点 6 (基地址 0x0770)</t>
         </is>
       </c>
-      <c r="B428" s="8" t="n"/>
-      <c r="C428" s="8" t="n"/>
-      <c r="D428" s="8" t="n"/>
-      <c r="E428" s="8" t="n"/>
-      <c r="F428" s="8" t="n"/>
-      <c r="G428" s="8" t="n"/>
-      <c r="H428" s="8" t="n"/>
+      <c r="B428" s="9" t="n"/>
+      <c r="C428" s="9" t="n"/>
+      <c r="D428" s="9" t="n"/>
+      <c r="E428" s="9" t="n"/>
+      <c r="F428" s="9" t="n"/>
+      <c r="G428" s="9" t="n"/>
+      <c r="H428" s="10" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="4" t="n">
@@ -19959,13 +20335,13 @@
           <t xml:space="preserve">  数据点 7 (基地址 0x0780)</t>
         </is>
       </c>
-      <c r="B442" s="8" t="n"/>
-      <c r="C442" s="8" t="n"/>
-      <c r="D442" s="8" t="n"/>
-      <c r="E442" s="8" t="n"/>
-      <c r="F442" s="8" t="n"/>
-      <c r="G442" s="8" t="n"/>
-      <c r="H442" s="8" t="n"/>
+      <c r="B442" s="9" t="n"/>
+      <c r="C442" s="9" t="n"/>
+      <c r="D442" s="9" t="n"/>
+      <c r="E442" s="9" t="n"/>
+      <c r="F442" s="9" t="n"/>
+      <c r="G442" s="9" t="n"/>
+      <c r="H442" s="10" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="4" t="n">
@@ -20467,13 +20843,13 @@
           <t>从机 4 (基地址 0x0900)</t>
         </is>
       </c>
-      <c r="B456" s="3" t="n"/>
-      <c r="C456" s="3" t="n"/>
-      <c r="D456" s="3" t="n"/>
-      <c r="E456" s="3" t="n"/>
-      <c r="F456" s="3" t="n"/>
-      <c r="G456" s="3" t="n"/>
-      <c r="H456" s="3" t="n"/>
+      <c r="B456" s="9" t="n"/>
+      <c r="C456" s="9" t="n"/>
+      <c r="D456" s="9" t="n"/>
+      <c r="E456" s="9" t="n"/>
+      <c r="F456" s="9" t="n"/>
+      <c r="G456" s="9" t="n"/>
+      <c r="H456" s="10" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="8" t="inlineStr">
@@ -20481,13 +20857,13 @@
           <t xml:space="preserve">  数据点 0 (基地址 0x0910)</t>
         </is>
       </c>
-      <c r="B457" s="8" t="n"/>
-      <c r="C457" s="8" t="n"/>
-      <c r="D457" s="8" t="n"/>
-      <c r="E457" s="8" t="n"/>
-      <c r="F457" s="8" t="n"/>
-      <c r="G457" s="8" t="n"/>
-      <c r="H457" s="8" t="n"/>
+      <c r="B457" s="9" t="n"/>
+      <c r="C457" s="9" t="n"/>
+      <c r="D457" s="9" t="n"/>
+      <c r="E457" s="9" t="n"/>
+      <c r="F457" s="9" t="n"/>
+      <c r="G457" s="9" t="n"/>
+      <c r="H457" s="10" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="4" t="n">
@@ -20989,13 +21365,13 @@
           <t xml:space="preserve">  数据点 1 (基地址 0x0920)</t>
         </is>
       </c>
-      <c r="B471" s="8" t="n"/>
-      <c r="C471" s="8" t="n"/>
-      <c r="D471" s="8" t="n"/>
-      <c r="E471" s="8" t="n"/>
-      <c r="F471" s="8" t="n"/>
-      <c r="G471" s="8" t="n"/>
-      <c r="H471" s="8" t="n"/>
+      <c r="B471" s="9" t="n"/>
+      <c r="C471" s="9" t="n"/>
+      <c r="D471" s="9" t="n"/>
+      <c r="E471" s="9" t="n"/>
+      <c r="F471" s="9" t="n"/>
+      <c r="G471" s="9" t="n"/>
+      <c r="H471" s="10" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="4" t="n">
@@ -21497,13 +21873,13 @@
           <t xml:space="preserve">  数据点 2 (基地址 0x0930)</t>
         </is>
       </c>
-      <c r="B485" s="8" t="n"/>
-      <c r="C485" s="8" t="n"/>
-      <c r="D485" s="8" t="n"/>
-      <c r="E485" s="8" t="n"/>
-      <c r="F485" s="8" t="n"/>
-      <c r="G485" s="8" t="n"/>
-      <c r="H485" s="8" t="n"/>
+      <c r="B485" s="9" t="n"/>
+      <c r="C485" s="9" t="n"/>
+      <c r="D485" s="9" t="n"/>
+      <c r="E485" s="9" t="n"/>
+      <c r="F485" s="9" t="n"/>
+      <c r="G485" s="9" t="n"/>
+      <c r="H485" s="10" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="4" t="n">
@@ -22005,13 +22381,13 @@
           <t xml:space="preserve">  数据点 3 (基地址 0x0940)</t>
         </is>
       </c>
-      <c r="B499" s="8" t="n"/>
-      <c r="C499" s="8" t="n"/>
-      <c r="D499" s="8" t="n"/>
-      <c r="E499" s="8" t="n"/>
-      <c r="F499" s="8" t="n"/>
-      <c r="G499" s="8" t="n"/>
-      <c r="H499" s="8" t="n"/>
+      <c r="B499" s="9" t="n"/>
+      <c r="C499" s="9" t="n"/>
+      <c r="D499" s="9" t="n"/>
+      <c r="E499" s="9" t="n"/>
+      <c r="F499" s="9" t="n"/>
+      <c r="G499" s="9" t="n"/>
+      <c r="H499" s="10" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="4" t="n">
@@ -22513,13 +22889,13 @@
           <t xml:space="preserve">  数据点 4 (基地址 0x0950)</t>
         </is>
       </c>
-      <c r="B513" s="8" t="n"/>
-      <c r="C513" s="8" t="n"/>
-      <c r="D513" s="8" t="n"/>
-      <c r="E513" s="8" t="n"/>
-      <c r="F513" s="8" t="n"/>
-      <c r="G513" s="8" t="n"/>
-      <c r="H513" s="8" t="n"/>
+      <c r="B513" s="9" t="n"/>
+      <c r="C513" s="9" t="n"/>
+      <c r="D513" s="9" t="n"/>
+      <c r="E513" s="9" t="n"/>
+      <c r="F513" s="9" t="n"/>
+      <c r="G513" s="9" t="n"/>
+      <c r="H513" s="10" t="n"/>
     </row>
     <row r="514">
       <c r="A514" s="4" t="n">
@@ -23021,13 +23397,13 @@
           <t xml:space="preserve">  数据点 5 (基地址 0x0960)</t>
         </is>
       </c>
-      <c r="B527" s="8" t="n"/>
-      <c r="C527" s="8" t="n"/>
-      <c r="D527" s="8" t="n"/>
-      <c r="E527" s="8" t="n"/>
-      <c r="F527" s="8" t="n"/>
-      <c r="G527" s="8" t="n"/>
-      <c r="H527" s="8" t="n"/>
+      <c r="B527" s="9" t="n"/>
+      <c r="C527" s="9" t="n"/>
+      <c r="D527" s="9" t="n"/>
+      <c r="E527" s="9" t="n"/>
+      <c r="F527" s="9" t="n"/>
+      <c r="G527" s="9" t="n"/>
+      <c r="H527" s="10" t="n"/>
     </row>
     <row r="528">
       <c r="A528" s="4" t="n">
@@ -23529,13 +23905,13 @@
           <t xml:space="preserve">  数据点 6 (基地址 0x0970)</t>
         </is>
       </c>
-      <c r="B541" s="8" t="n"/>
-      <c r="C541" s="8" t="n"/>
-      <c r="D541" s="8" t="n"/>
-      <c r="E541" s="8" t="n"/>
-      <c r="F541" s="8" t="n"/>
-      <c r="G541" s="8" t="n"/>
-      <c r="H541" s="8" t="n"/>
+      <c r="B541" s="9" t="n"/>
+      <c r="C541" s="9" t="n"/>
+      <c r="D541" s="9" t="n"/>
+      <c r="E541" s="9" t="n"/>
+      <c r="F541" s="9" t="n"/>
+      <c r="G541" s="9" t="n"/>
+      <c r="H541" s="10" t="n"/>
     </row>
     <row r="542">
       <c r="A542" s="4" t="n">
@@ -24037,13 +24413,13 @@
           <t xml:space="preserve">  数据点 7 (基地址 0x0980)</t>
         </is>
       </c>
-      <c r="B555" s="8" t="n"/>
-      <c r="C555" s="8" t="n"/>
-      <c r="D555" s="8" t="n"/>
-      <c r="E555" s="8" t="n"/>
-      <c r="F555" s="8" t="n"/>
-      <c r="G555" s="8" t="n"/>
-      <c r="H555" s="8" t="n"/>
+      <c r="B555" s="9" t="n"/>
+      <c r="C555" s="9" t="n"/>
+      <c r="D555" s="9" t="n"/>
+      <c r="E555" s="9" t="n"/>
+      <c r="F555" s="9" t="n"/>
+      <c r="G555" s="9" t="n"/>
+      <c r="H555" s="10" t="n"/>
     </row>
     <row r="556">
       <c r="A556" s="4" t="n">
@@ -24546,13 +24922,13 @@
     <mergeCell ref="A358:H358"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A216:H216"/>
+    <mergeCell ref="A132:H132"/>
     <mergeCell ref="A103:H103"/>
-    <mergeCell ref="A132:H132"/>
+    <mergeCell ref="A527:H527"/>
     <mergeCell ref="A287:H287"/>
+    <mergeCell ref="A343:H343"/>
     <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A343:H343"/>
     <mergeCell ref="A315:H315"/>
-    <mergeCell ref="A527:H527"/>
     <mergeCell ref="A146:H146"/>
     <mergeCell ref="A457:H457"/>
     <mergeCell ref="A471:H471"/>
@@ -24598,7 +24974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -24642,9 +25018,9 @@
           <t>通信参数</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -24718,9 +25094,9 @@
           <t>设备信息</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -24794,9 +25170,9 @@
           <t>上报配置</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -24848,9 +25224,9 @@
           <t>从机配置 (以从机0为例)</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -24968,9 +25344,9 @@
           <t>数据点配置 (以从机0-数据点0为例)</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -25060,12 +25436,67 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>设备状态</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>设备运行时间</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>0x0016 + 0x0017</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>— (只读)</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>单位: 秒, 32位无符号, 溢出周期 ~136年</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>预留寄存器</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>0x0018~0x001F</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>— (只读)</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>8 个预留位, 返回 0, 未来扩展用</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="A15:D15"/>
   </mergeCells>

--- a/docs/STM32L051_Modbus_配置地址表_v2.3.xlsx
+++ b/docs/STM32L051_Modbus_配置地址表_v2.3.xlsx
@@ -550,6 +550,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1340,11 +1341,11 @@
           <t>设备运行状态</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -1416,11 +1417,11 @@
           <t>预留寄存器 (未来扩展)</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -1430,12 +1431,12 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>reserved[0]</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>sleep_interval_sec</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>RW</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -1445,12 +1446,12 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0~65535</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>预留 #0 (只读, 返回 0)</t>
+          <t>低功耗休眠间隔 (秒), 0=禁用</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1483,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>预留 #1</t>
+          <t>预留 #1 (只读, 返回 0)</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1515,7 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>预留 #2</t>
+          <t>预留 #2 (只读, 返回 0)</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1547,7 @@
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>预留 #3</t>
+          <t>预留 #3 (只读, 返回 0)</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1579,7 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>预留 #4</t>
+          <t>预留 #4 (只读, 返回 0)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1611,7 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>预留 #5</t>
+          <t>预留 #5 (只读, 返回 0)</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1643,7 @@
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>预留 #6</t>
+          <t>预留 #6 (只读, 返回 0)</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1675,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>预留 #7</t>
+          <t>预留 #7 (只读, 返回 0)</t>
         </is>
       </c>
     </row>
@@ -24974,7 +24975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -25442,9 +25443,9 @@
           <t>设备状态</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -25487,6 +25488,28 @@
       <c r="D28" s="6" t="inlineStr">
         <is>
           <t>8 个预留位, 返回 0, 未来扩展用</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>低功耗休眠间隔</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>0x0018</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>0x0018</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>0=禁用, 1~65535=休眠秒数</t>
         </is>
       </c>
     </row>
